--- a/figures/multiple_datasets_pretrain.xlsx
+++ b/figures/multiple_datasets_pretrain.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="27660" activeTab="5"/>
+    <workbookView windowWidth="32460" windowHeight="15660" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="mre" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="19">
   <si>
     <t>settings</t>
   </si>
@@ -56,6 +56,39 @@
   </si>
   <si>
     <t>setting 3</t>
+  </si>
+  <si>
+    <t>4106751954.6385</t>
+  </si>
+  <si>
+    <t>1.8891164064407349</t>
+  </si>
+  <si>
+    <t>1.2428776621818542</t>
+  </si>
+  <si>
+    <t>5.7897865772247314</t>
+  </si>
+  <si>
+    <t>2.7088670730590767</t>
+  </si>
+  <si>
+    <t>143572591963100299264.0000</t>
+  </si>
+  <si>
+    <t>2469999990013952.0000</t>
+  </si>
+  <si>
+    <t>8.996321678161621</t>
+  </si>
+  <si>
+    <t>8.787158012390137</t>
+  </si>
+  <si>
+    <t>119632524283461776.0000</t>
+  </si>
+  <si>
+    <t>486913245184.0000</t>
   </si>
 </sst>
 </file>
@@ -682,6 +715,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1284,16 +1320,16 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>0.9829</v>
+        <v>1.2811</v>
       </c>
       <c r="C4" s="2">
-        <v>0.5958</v>
+        <v>0.4901</v>
       </c>
       <c r="D4" s="2">
-        <v>0.7217895</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.29882497</v>
+        <v>0.70694274</v>
+      </c>
+      <c r="E4">
+        <v>0.37536356</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
@@ -1585,17 +1621,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>3268219183.4624</v>
-      </c>
-      <c r="C4" s="2">
-        <v>36063.8672</v>
-      </c>
-      <c r="D4" s="2">
-        <v>52551.695</v>
-      </c>
-      <c r="E4" s="2">
-        <v>35930.93</v>
+      <c r="B4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>62737.9453</v>
+      </c>
+      <c r="D4">
+        <v>51084.863</v>
+      </c>
+      <c r="E4">
+        <v>29615.59</v>
       </c>
     </row>
   </sheetData>
@@ -1668,17 +1704,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>1.7458</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.7255</v>
-      </c>
-      <c r="D4" s="2">
-        <v>1.84465169906616</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.25500178337097</v>
+      <c r="B4">
+        <v>2.0184</v>
+      </c>
+      <c r="C4">
+        <v>1.4302</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1752,17 +1788,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>3.5898</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2.545</v>
-      </c>
-      <c r="D4" s="2">
-        <v>5.42536311149597</v>
-      </c>
-      <c r="E4" s="2">
-        <v>2.4482266664505</v>
+      <c r="B4">
+        <v>4.9184</v>
+      </c>
+      <c r="C4">
+        <v>5.4203</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1836,17 +1872,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>1.4790020722532e+19</v>
-      </c>
-      <c r="C4" s="2">
-        <v>4.6491</v>
-      </c>
-      <c r="D4" s="2">
-        <v>7.3677978515625</v>
-      </c>
-      <c r="E4" s="2">
-        <v>4.86568450927734</v>
+      <c r="B4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1921,17 +1957,17 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2">
-        <v>1.17964612033003e+16</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.7383</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2.4187465</v>
-      </c>
-      <c r="E4" s="2">
-        <v>1.4358183</v>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>2.3628426</v>
+      </c>
+      <c r="E4">
+        <v>1.532851</v>
       </c>
     </row>
   </sheetData>

--- a/figures/multiple_datasets_pretrain.xlsx
+++ b/figures/multiple_datasets_pretrain.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32460" windowHeight="15660" activeTab="5"/>
+    <workbookView windowHeight="15660" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="mre" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
   <si>
     <t>settings</t>
   </si>
@@ -55,40 +55,100 @@
     <t>setting 2</t>
   </si>
   <si>
+    <t>1677090176.0000</t>
+  </si>
+  <si>
     <t>setting 3</t>
   </si>
   <si>
-    <t>4106751954.6385</t>
-  </si>
-  <si>
-    <t>1.8891164064407349</t>
-  </si>
-  <si>
-    <t>1.2428776621818542</t>
-  </si>
-  <si>
-    <t>5.7897865772247314</t>
-  </si>
-  <si>
-    <t>2.7088670730590767</t>
-  </si>
-  <si>
-    <t>143572591963100299264.0000</t>
-  </si>
-  <si>
-    <t>2469999990013952.0000</t>
-  </si>
-  <si>
-    <t>8.996321678161621</t>
-  </si>
-  <si>
-    <t>8.787158012390137</t>
-  </si>
-  <si>
-    <t>119632524283461776.0000</t>
-  </si>
-  <si>
-    <t>486913245184.0000</t>
+    <t>10500203287.9570</t>
+  </si>
+  <si>
+    <t>9918028631.8739</t>
+  </si>
+  <si>
+    <t>38590358463971328.0000</t>
+  </si>
+  <si>
+    <t>8879057252.9838</t>
+  </si>
+  <si>
+    <t>4444174848.0000</t>
+  </si>
+  <si>
+    <t>1.7177928686141968</t>
+  </si>
+  <si>
+    <t>1.4969592690467834</t>
+  </si>
+  <si>
+    <t>1.5626710653305054</t>
+  </si>
+  <si>
+    <t>1.220563530921936</t>
+  </si>
+  <si>
+    <t>1.5110614895820618</t>
+  </si>
+  <si>
+    <t>1.2596327066421509</t>
+  </si>
+  <si>
+    <t>11.027849149703975</t>
+  </si>
+  <si>
+    <t>12.162946701049805</t>
+  </si>
+  <si>
+    <t>4.247394537925719</t>
+  </si>
+  <si>
+    <t>10.630474996566765</t>
+  </si>
+  <si>
+    <t>4.7106329441070445</t>
+  </si>
+  <si>
+    <t>5.680100345611571</t>
+  </si>
+  <si>
+    <t>158382405605368102912.0000</t>
+  </si>
+  <si>
+    <t>1865759965839360.0</t>
+  </si>
+  <si>
+    <t>48.4032096862793</t>
+  </si>
+  <si>
+    <t>1478971753733609226240.0000</t>
+  </si>
+  <si>
+    <t>13086265180160.0000</t>
+  </si>
+  <si>
+    <t>393.8269958496094</t>
+  </si>
+  <si>
+    <t>238.47447204589844</t>
+  </si>
+  <si>
+    <t>58479991579208368128.0000</t>
+  </si>
+  <si>
+    <t>49.665428161621094</t>
+  </si>
+  <si>
+    <t>33.33909606933594</t>
+  </si>
+  <si>
+    <t>4134578042664130.5000</t>
+  </si>
+  <si>
+    <t>70277947645688768.0000</t>
+  </si>
+  <si>
+    <t>5384838988831963.0000</t>
   </si>
 </sst>
 </file>
@@ -1279,17 +1339,17 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>1.1688</v>
-      </c>
-      <c r="C2" s="2">
-        <v>0.6256</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3281.777</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1.1434686</v>
+      <c r="B2">
+        <v>0.9808</v>
+      </c>
+      <c r="C2">
+        <v>11.3607</v>
+      </c>
+      <c r="D2">
+        <v>0.6402181</v>
+      </c>
+      <c r="E2">
+        <v>0.5206813</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1299,17 +1359,17 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>0.4931</v>
-      </c>
-      <c r="C3" s="2">
-        <v>0.6701</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0.5384948</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0.26294875</v>
+      <c r="B3">
+        <v>2.139</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>0.9154991</v>
+      </c>
+      <c r="E3">
+        <v>0.29058138</v>
       </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -1317,19 +1377,19 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2">
-        <v>1.2811</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0.4901</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.70694274</v>
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>0.8255</v>
+      </c>
+      <c r="C4">
+        <v>182.9268</v>
+      </c>
+      <c r="D4">
+        <v>0.50855976</v>
       </c>
       <c r="E4">
-        <v>0.37536356</v>
+        <v>0.33843556</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="2"/>
@@ -1587,51 +1647,51 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>4933557917.7314</v>
-      </c>
-      <c r="C2" s="2">
-        <v>81959.8203</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4090131700</v>
-      </c>
-      <c r="E2" s="2">
-        <v>60239.836</v>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>8793507</v>
+      </c>
+      <c r="D2">
+        <v>165949.92</v>
+      </c>
+      <c r="E2">
+        <v>166667.22</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>6123104968.3147</v>
-      </c>
-      <c r="C3" s="2">
-        <v>88120.4844</v>
-      </c>
-      <c r="D3" s="2">
-        <v>49683.926</v>
-      </c>
-      <c r="E3" s="2">
-        <v>13126.689</v>
+      <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>125466.09</v>
+      </c>
+      <c r="E3">
+        <v>98046.836</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>62737.9453</v>
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="D4">
-        <v>51084.863</v>
+        <v>127853.06</v>
       </c>
       <c r="E4">
-        <v>29615.59</v>
+        <v>128532.02</v>
       </c>
     </row>
   </sheetData>
@@ -1670,51 +1730,51 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>1.712</v>
-      </c>
-      <c r="C2" s="2">
-        <v>3.288</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2.01969039440155</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1.75030523538589</v>
+      <c r="B2">
+        <v>1.6921</v>
+      </c>
+      <c r="C2">
+        <v>14.169</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>2.1396</v>
-      </c>
-      <c r="C3" s="2">
-        <v>4.2511</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1.81156545877456</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1.18075013160705</v>
+      <c r="B3">
+        <v>1.4945</v>
+      </c>
+      <c r="C3">
+        <v>1.4272</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>2.0184</v>
+        <v>1.4047</v>
       </c>
       <c r="C4">
-        <v>1.4302</v>
+        <v>6.8598</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1754,51 +1814,51 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>5.6213</v>
-      </c>
-      <c r="C2" s="2">
-        <v>5.4908</v>
-      </c>
-      <c r="D2" s="2">
-        <v>9.20867838859559</v>
-      </c>
-      <c r="E2" s="2">
-        <v>5.9148508310318</v>
+      <c r="B2">
+        <v>5.2482</v>
+      </c>
+      <c r="C2">
+        <v>18.393</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>4.5724</v>
-      </c>
-      <c r="C3" s="2">
-        <v>8.003</v>
-      </c>
-      <c r="D3" s="2">
-        <v>3.22825491428375</v>
-      </c>
-      <c r="E3" s="2">
-        <v>2.21420814990997</v>
+      <c r="B3">
+        <v>10.377</v>
+      </c>
+      <c r="C3">
+        <v>10.3556</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>4.9184</v>
+        <v>5.1264</v>
       </c>
       <c r="C4">
-        <v>5.4203</v>
+        <v>9.3295</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1838,51 +1898,51 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>41.5113</v>
-      </c>
-      <c r="C2" s="2">
-        <v>8.2808</v>
-      </c>
-      <c r="D2" s="2">
-        <v>15207578</v>
-      </c>
-      <c r="E2" s="3">
-        <v>31.2644710540771</v>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>3345.0667</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>33.8695</v>
-      </c>
-      <c r="C3" s="2">
-        <v>9.8093</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1347079985168380</v>
-      </c>
-      <c r="E3" s="2">
-        <v>5.7931432723999</v>
+      <c r="B3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>33</v>
+      </c>
+      <c r="C4">
+        <v>766706.5</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1923,51 +1983,51 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
-        <v>2.2861</v>
-      </c>
-      <c r="C2" s="2">
-        <v>3.3626</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3282.8464</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2.5056512</v>
+      <c r="B2" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2">
+        <v>12.3842</v>
+      </c>
+      <c r="D2">
+        <v>229682660000</v>
+      </c>
+      <c r="E2">
+        <v>3.5896282</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2">
-        <v>2.4963</v>
-      </c>
-      <c r="C3" s="2">
-        <v>4.2891</v>
-      </c>
-      <c r="D3" s="2">
-        <v>765664030000</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1.3368454</v>
+      <c r="B3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>2.0831587</v>
+      </c>
+      <c r="E3">
+        <v>2.376486</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>183.9764</v>
       </c>
       <c r="D4">
-        <v>2.3628426</v>
+        <v>2.1292052</v>
       </c>
       <c r="E4">
-        <v>1.532851</v>
+        <v>2.0591688</v>
       </c>
     </row>
   </sheetData>
